--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_9.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0287662035051537</v>
+        <v>0.02406051033690499</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008444211796812763</v>
+        <v>0.008438734620987253</v>
       </c>
       <c r="C2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>39068950</v>
+        <v>4082171</v>
       </c>
       <c r="L2" t="n">
-        <v>20510194</v>
+        <v>1834922</v>
       </c>
       <c r="M2" t="n">
-        <v>4737459</v>
+        <v>371358</v>
       </c>
       <c r="N2" t="n">
-        <v>217218</v>
+        <v>8917</v>
       </c>
       <c r="O2" t="n">
-        <v>2810571</v>
+        <v>193589</v>
       </c>
       <c r="P2" t="n">
-        <v>1148171</v>
+        <v>79138</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999906420707703</v>
+        <v>0.9999944567680359</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8333993554115295</v>
+        <v>0.754180371761322</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6921908259391785</v>
+        <v>0.5742262005805969</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6151659488677979</v>
+        <v>0.4586212337017059</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2182044982910156</v>
+        <v>0.05866717547178268</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6754528880119324</v>
+        <v>0.5115001797676086</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7669454216957092</v>
+        <v>0.6529645919799805</v>
       </c>
       <c r="X2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>57267729</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>43599582</v>
+        <v>4801660</v>
       </c>
       <c r="AG2" t="n">
-        <v>27067956</v>
+        <v>3018155</v>
       </c>
       <c r="AH2" t="n">
-        <v>7231912</v>
+        <v>805700</v>
       </c>
       <c r="AI2" t="n">
-        <v>533313</v>
+        <v>59334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4140105</v>
+        <v>460847</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621484</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560521245002747</v>
+        <v>0.9551666378974915</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115551710128784</v>
+        <v>0.9119651317596436</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579047322273254</v>
+        <v>0.8582442998886108</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615177989006042</v>
+        <v>0.660926342010498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019250869750977</v>
+        <v>0.9019715189933777</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314548373222351</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.007401974469572342</v>
+        <v>0.006051152956823311</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002022735960981907</v>
+        <v>0.002022102987121896</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>39068950</v>
+        <v>4082171</v>
       </c>
       <c r="E3" t="n">
-        <v>6228920</v>
+        <v>892499</v>
       </c>
       <c r="F3" t="n">
-        <v>198249</v>
+        <v>35280</v>
       </c>
       <c r="G3" t="n">
-        <v>24419</v>
+        <v>3227</v>
       </c>
       <c r="H3" t="n">
-        <v>12491</v>
+        <v>1883</v>
       </c>
       <c r="I3" t="n">
-        <v>1024</v>
+        <v>162</v>
       </c>
       <c r="J3" t="n">
-        <v>90864535</v>
+        <v>10069585</v>
       </c>
       <c r="K3" t="n">
-        <v>94788639</v>
+        <v>10070220</v>
       </c>
       <c r="L3" t="n">
-        <v>109261403</v>
+        <v>11736659</v>
       </c>
       <c r="M3" t="n">
-        <v>136730443</v>
+        <v>15036995</v>
       </c>
       <c r="N3" t="n">
-        <v>146547578</v>
+        <v>16183047</v>
       </c>
       <c r="O3" t="n">
-        <v>142189143</v>
+        <v>15719715</v>
       </c>
       <c r="P3" t="n">
-        <v>146042551</v>
+        <v>16180254</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8580154776573181</v>
+        <v>0.813955545425415</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6894007921218872</v>
+        <v>0.5528882145881653</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5613961815834045</v>
+        <v>0.3947945833206177</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2691802978515625</v>
+        <v>0.0992133691906929</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6118967533111572</v>
+        <v>0.3785463869571686</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6593568325042725</v>
+        <v>0.4085891544818878</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43599582</v>
+        <v>4801660</v>
       </c>
       <c r="Z3" t="n">
-        <v>1794818</v>
+        <v>198183</v>
       </c>
       <c r="AA3" t="n">
-        <v>77289</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>61790</v>
+        <v>6873</v>
       </c>
       <c r="AC3" t="n">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90865071</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>100594524</v>
+        <v>11175395</v>
       </c>
       <c r="AG3" t="n">
-        <v>115755743</v>
+        <v>12805854</v>
       </c>
       <c r="AH3" t="n">
-        <v>138496265</v>
+        <v>15342287</v>
       </c>
       <c r="AI3" t="n">
-        <v>147052956</v>
+        <v>16295683</v>
       </c>
       <c r="AJ3" t="n">
-        <v>143089396</v>
+        <v>15854513</v>
       </c>
       <c r="AK3" t="n">
-        <v>146272126</v>
+        <v>16209047</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575152397155762</v>
+        <v>0.9574164748191833</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098241925239563</v>
+        <v>0.9094131588935852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569927215576172</v>
+        <v>0.8565481305122375</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608906984329224</v>
+        <v>0.6601688861846924</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901353120803833</v>
+        <v>0.9011460542678833</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311649203300476</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06637520463369279</v>
+        <v>0.05723192500171009</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03194306376401414</v>
+        <v>0.03192845045564235</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>7257323</v>
+        <v>1216979</v>
       </c>
       <c r="E4" t="n">
-        <v>20510194</v>
+        <v>1834922</v>
       </c>
       <c r="F4" t="n">
-        <v>1664578</v>
+        <v>216378</v>
       </c>
       <c r="G4" t="n">
-        <v>120260</v>
+        <v>20921</v>
       </c>
       <c r="H4" t="n">
-        <v>177149</v>
+        <v>26100</v>
       </c>
       <c r="I4" t="n">
-        <v>21228</v>
+        <v>3489</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>7810075</v>
+        <v>1330554</v>
       </c>
       <c r="L4" t="n">
-        <v>9120643</v>
+        <v>1360547</v>
       </c>
       <c r="M4" t="n">
-        <v>2963648</v>
+        <v>438369</v>
       </c>
       <c r="N4" t="n">
-        <v>778261</v>
+        <v>143076</v>
       </c>
       <c r="O4" t="n">
-        <v>1350446</v>
+        <v>184884</v>
       </c>
       <c r="P4" t="n">
-        <v>348899</v>
+        <v>42060</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999952912330627</v>
+        <v>0.9999971985816956</v>
       </c>
       <c r="R4" t="n">
-        <v>0.845528244972229</v>
+        <v>0.7829286456108093</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6907930374145508</v>
+        <v>0.5633552074432373</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5870524644851685</v>
+        <v>0.4243211150169373</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2410265952348709</v>
+        <v>0.07373382151126862</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6421059370040894</v>
+        <v>0.4350930452346802</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7090933322906494</v>
+        <v>0.502648651599884</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1871575</v>
+        <v>210622</v>
       </c>
       <c r="Z4" t="n">
-        <v>27067956</v>
+        <v>3018155</v>
       </c>
       <c r="AA4" t="n">
-        <v>750277</v>
+        <v>83217</v>
       </c>
       <c r="AB4" t="n">
-        <v>50035</v>
+        <v>5601</v>
       </c>
       <c r="AC4" t="n">
-        <v>10299</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2004190</v>
+        <v>225379</v>
       </c>
       <c r="AG4" t="n">
-        <v>2626303</v>
+        <v>291352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1197826</v>
+        <v>133077</v>
       </c>
       <c r="AI4" t="n">
-        <v>272883</v>
+        <v>30440</v>
       </c>
       <c r="AJ4" t="n">
-        <v>450193</v>
+        <v>50086</v>
       </c>
       <c r="AK4" t="n">
-        <v>119324</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567831754684448</v>
+        <v>0.9562901854515076</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106888175010681</v>
+        <v>0.9106873869895935</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574485182762146</v>
+        <v>0.857395350933075</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612040996551514</v>
+        <v>0.6605474352836609</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016390442848206</v>
+        <v>0.9015586376190186</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313098192214966</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>392023</v>
+        <v>84402</v>
       </c>
       <c r="E5" t="n">
-        <v>2363528</v>
+        <v>365745</v>
       </c>
       <c r="F5" t="n">
-        <v>4737459</v>
+        <v>371358</v>
       </c>
       <c r="G5" t="n">
-        <v>255086</v>
+        <v>39318</v>
       </c>
       <c r="H5" t="n">
-        <v>617600</v>
+        <v>68983</v>
       </c>
       <c r="I5" t="n">
-        <v>72963</v>
+        <v>10825</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6465136</v>
+        <v>933055</v>
       </c>
       <c r="L5" t="n">
-        <v>9240560</v>
+        <v>1483872</v>
       </c>
       <c r="M5" t="n">
-        <v>3701250</v>
+        <v>569278</v>
       </c>
       <c r="N5" t="n">
-        <v>589743</v>
+        <v>80960</v>
       </c>
       <c r="O5" t="n">
-        <v>1782640</v>
+        <v>317812</v>
       </c>
       <c r="P5" t="n">
-        <v>593179</v>
+        <v>114548</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999963641166687</v>
+        <v>0.9999978542327881</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9036323428153992</v>
+        <v>0.8621096014976501</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8760490417480469</v>
+        <v>0.826728880405426</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9550072550773621</v>
+        <v>0.938618004322052</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9907650351524353</v>
+        <v>0.9863525629043579</v>
       </c>
       <c r="V5" t="n">
-        <v>0.978849470615387</v>
+        <v>0.9693776965141296</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936403036117554</v>
+        <v>0.9904600381851196</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>73158</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>774906</v>
+        <v>86892</v>
       </c>
       <c r="AA5" t="n">
-        <v>7231912</v>
+        <v>805700</v>
       </c>
       <c r="AB5" t="n">
-        <v>90018</v>
+        <v>10028</v>
       </c>
       <c r="AC5" t="n">
-        <v>263018</v>
+        <v>29263</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1934504</v>
+        <v>213566</v>
       </c>
       <c r="AG5" t="n">
-        <v>2682798</v>
+        <v>300639</v>
       </c>
       <c r="AH5" t="n">
-        <v>1206797</v>
+        <v>134936</v>
       </c>
       <c r="AI5" t="n">
-        <v>273648</v>
+        <v>30543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>453106</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119866</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734110832214355</v>
+        <v>0.9732611179351807</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641598463058472</v>
+        <v>0.9639381766319275</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837670922279358</v>
+        <v>0.9836736917495728</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963105320930481</v>
+        <v>0.9962851405143738</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939020872116089</v>
+        <v>0.993869423866272</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983853101730347</v>
+        <v>0.998377799987793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>128007</v>
+        <v>19805</v>
       </c>
       <c r="E6" t="n">
-        <v>174021</v>
+        <v>24606</v>
       </c>
       <c r="F6" t="n">
-        <v>190569</v>
+        <v>27485</v>
       </c>
       <c r="G6" t="n">
-        <v>217218</v>
+        <v>8917</v>
       </c>
       <c r="H6" t="n">
-        <v>85748</v>
+        <v>7791</v>
       </c>
       <c r="I6" t="n">
-        <v>11304</v>
+        <v>1266</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58973</v>
+        <v>6601</v>
       </c>
       <c r="Z6" t="n">
-        <v>48553</v>
+        <v>5386</v>
       </c>
       <c r="AA6" t="n">
-        <v>98760</v>
+        <v>11048</v>
       </c>
       <c r="AB6" t="n">
-        <v>533313</v>
+        <v>59334</v>
       </c>
       <c r="AC6" t="n">
-        <v>63033</v>
+        <v>7027</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>31418</v>
+        <v>9067</v>
       </c>
       <c r="E7" t="n">
-        <v>324075</v>
+        <v>70161</v>
       </c>
       <c r="F7" t="n">
-        <v>845900</v>
+        <v>143704</v>
       </c>
       <c r="G7" t="n">
-        <v>338717</v>
+        <v>68557</v>
       </c>
       <c r="H7" t="n">
-        <v>2810571</v>
+        <v>193589</v>
       </c>
       <c r="I7" t="n">
-        <v>242380</v>
+        <v>26318</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>232</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7297</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>268516</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68645</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4140105</v>
+        <v>460847</v>
       </c>
       <c r="AD7" t="n">
-        <v>108416</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>187</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1304</v>
+        <v>301</v>
       </c>
       <c r="E8" t="n">
-        <v>30099</v>
+        <v>7536</v>
       </c>
       <c r="F8" t="n">
-        <v>64352</v>
+        <v>15522</v>
       </c>
       <c r="G8" t="n">
-        <v>39779</v>
+        <v>11053</v>
       </c>
       <c r="H8" t="n">
-        <v>457458</v>
+        <v>80127</v>
       </c>
       <c r="I8" t="n">
-        <v>1148171</v>
+        <v>79138</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2984</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2395</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113506</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621484</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
